--- a/Data/Bystrategi_Grenland/Klima/Luftforurensing/PM10 og NO2 døgn mars-mai 2026.xlsx
+++ b/Data/Bystrategi_Grenland/Klima/Luftforurensing/PM10 og NO2 døgn mars-mai 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://telemarkfylke-my.sharepoint.com/personal/even_sannes_riiser_telemarkfylke_no/Documents/Github/Telemark/Data/Bystrategi_Grenland/Klima/Luftforurensing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{28373EBB-3F05-46B8-8A76-9C2E7C7D99F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41010519-91E1-4826-AD59-4FB6688A0F75}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{28373EBB-3F05-46B8-8A76-9C2E7C7D99F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C249BB82-D03B-4430-9CC8-F7962A2CB31B}"/>
   <bookViews>
-    <workbookView xWindow="38295" yWindow="0" windowWidth="38610" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19740" yWindow="0" windowWidth="37290" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -402,6 +402,7 @@
     <col min="7" max="7" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="24.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
